--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121003077</v>
+        <v>121001617</v>
       </c>
       <c r="B3" t="n">
-        <v>79715</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550156</v>
+        <v>550137</v>
       </c>
       <c r="R3" t="n">
-        <v>6994109</v>
+        <v>6994152</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,11 +875,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +905,7 @@
         <v>121003623</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1018,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121003046</v>
+        <v>121003233</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>90662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550156</v>
+        <v>550151</v>
       </c>
       <c r="R5" t="n">
-        <v>6994109</v>
+        <v>6994084</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1097,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121003107</v>
+        <v>121002081</v>
       </c>
       <c r="B6" t="n">
-        <v>79639</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550156</v>
+        <v>550141</v>
       </c>
       <c r="R6" t="n">
-        <v>6994109</v>
+        <v>6994157</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1202,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121004243</v>
+        <v>121003862</v>
       </c>
       <c r="B7" t="n">
-        <v>90687</v>
+        <v>79711</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550240</v>
+        <v>550193</v>
       </c>
       <c r="R7" t="n">
-        <v>6994134</v>
+        <v>6994068</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,6 +1309,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121002784</v>
+        <v>121004243</v>
       </c>
       <c r="B8" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550165</v>
+        <v>550240</v>
       </c>
       <c r="R8" t="n">
-        <v>6994154</v>
+        <v>6994134</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1455,7 +1450,7 @@
         <v>121001866</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>79711</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1563,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121003862</v>
+        <v>121003107</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>79642</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1574,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550193</v>
+        <v>550156</v>
       </c>
       <c r="R10" t="n">
-        <v>6994068</v>
+        <v>6994109</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1641,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121002900</v>
+        <v>121003077</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>79718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1681,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1717,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550164</v>
+        <v>550156</v>
       </c>
       <c r="R11" t="n">
-        <v>6994129</v>
+        <v>6994109</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,6 +1748,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121003233</v>
+        <v>121003046</v>
       </c>
       <c r="B12" t="n">
-        <v>90652</v>
+        <v>79682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550151</v>
+        <v>550156</v>
       </c>
       <c r="R12" t="n">
-        <v>6994084</v>
+        <v>6994109</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1859,6 +1859,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121002972</v>
+        <v>121001781</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1929,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550152</v>
+        <v>550136</v>
       </c>
       <c r="R13" t="n">
-        <v>6994109</v>
+        <v>6994142</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1969,7 +1974,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,7 +2005,7 @@
         <v>121003793</v>
       </c>
       <c r="B14" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121001617</v>
+        <v>121002784</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,21 +2129,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550137</v>
+        <v>550165</v>
       </c>
       <c r="R15" t="n">
-        <v>6994152</v>
+        <v>6994154</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2214,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121003973</v>
+        <v>121002900</v>
       </c>
       <c r="B16" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550184</v>
+        <v>550164</v>
       </c>
       <c r="R16" t="n">
-        <v>6994074</v>
+        <v>6994129</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2320,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121002081</v>
+        <v>121002972</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,10 +2368,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550141</v>
+        <v>550152</v>
       </c>
       <c r="R17" t="n">
-        <v>6994157</v>
+        <v>6994109</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2403,7 +2408,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2436,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121001781</v>
+        <v>121003973</v>
       </c>
       <c r="B18" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550136</v>
+        <v>550184</v>
       </c>
       <c r="R18" t="n">
-        <v>6994142</v>
+        <v>6994074</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2510,11 +2515,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,10 +2542,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121004113</v>
+        <v>121003525</v>
       </c>
       <c r="B19" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550183</v>
+        <v>550173</v>
       </c>
       <c r="R19" t="n">
-        <v>6994078</v>
+        <v>6994064</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121002758</v>
+        <v>121003368</v>
       </c>
       <c r="B20" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550165</v>
+        <v>550164</v>
       </c>
       <c r="R20" t="n">
-        <v>6994154</v>
+        <v>6994073</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121004238</v>
+        <v>121002529</v>
       </c>
       <c r="B21" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550211</v>
+        <v>550155</v>
       </c>
       <c r="R21" t="n">
-        <v>6994140</v>
+        <v>6994168</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2836,6 +2836,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rik förekomst inom ca 1 x 1 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,10 +2868,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121003525</v>
+        <v>121002758</v>
       </c>
       <c r="B22" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2907,10 +2912,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550173</v>
+        <v>550165</v>
       </c>
       <c r="R22" t="n">
-        <v>6994064</v>
+        <v>6994154</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2970,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121003368</v>
+        <v>121004238</v>
       </c>
       <c r="B23" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3014,10 +3019,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550164</v>
+        <v>550211</v>
       </c>
       <c r="R23" t="n">
-        <v>6994073</v>
+        <v>6994140</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3077,10 +3082,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121002529</v>
+        <v>121004113</v>
       </c>
       <c r="B24" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3121,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550155</v>
+        <v>550183</v>
       </c>
       <c r="R24" t="n">
-        <v>6994168</v>
+        <v>6994078</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3157,11 +3162,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rik förekomst inom ca 1 x 1 meter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121003824</v>
+        <v>121004241</v>
       </c>
       <c r="B25" t="n">
-        <v>79714</v>
+        <v>90983</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3201,25 +3201,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550193</v>
+        <v>550240</v>
       </c>
       <c r="R25" t="n">
-        <v>6994068</v>
+        <v>6994134</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3268,11 +3268,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3295,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004241</v>
+        <v>121003824</v>
       </c>
       <c r="B26" t="n">
-        <v>90973</v>
+        <v>79717</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3312,25 +3307,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3338,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550240</v>
+        <v>550193</v>
       </c>
       <c r="R26" t="n">
-        <v>6994134</v>
+        <v>6994068</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3379,6 +3374,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121001617</v>
+        <v>121003623</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550137</v>
+        <v>550173</v>
       </c>
       <c r="R3" t="n">
-        <v>6994152</v>
+        <v>6994058</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,6 +875,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121003623</v>
+        <v>121003793</v>
       </c>
       <c r="B4" t="n">
         <v>79682</v>
@@ -945,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550173</v>
+        <v>550193</v>
       </c>
       <c r="R4" t="n">
-        <v>6994058</v>
+        <v>6994068</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,7 +990,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121003233</v>
+        <v>121003046</v>
       </c>
       <c r="B5" t="n">
-        <v>90662</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550151</v>
+        <v>550156</v>
       </c>
       <c r="R5" t="n">
-        <v>6994084</v>
+        <v>6994109</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,6 +1097,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121002081</v>
+        <v>121002900</v>
       </c>
       <c r="B6" t="n">
         <v>78601</v>
@@ -1162,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550141</v>
+        <v>550164</v>
       </c>
       <c r="R6" t="n">
-        <v>6994157</v>
+        <v>6994129</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,11 +1208,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1341,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121004243</v>
+        <v>121003107</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>79642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1358,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550240</v>
+        <v>550156</v>
       </c>
       <c r="R8" t="n">
-        <v>6994134</v>
+        <v>6994109</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,6 +1425,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121001866</v>
+        <v>121002081</v>
       </c>
       <c r="B9" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,25 +1469,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550136</v>
+        <v>550141</v>
       </c>
       <c r="R9" t="n">
-        <v>6994142</v>
+        <v>6994157</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1530,7 +1540,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På asp tillsammans med lunglav</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121003107</v>
+        <v>121001617</v>
       </c>
       <c r="B10" t="n">
-        <v>79642</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,25 +1580,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550156</v>
+        <v>550137</v>
       </c>
       <c r="R10" t="n">
-        <v>6994109</v>
+        <v>6994152</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1637,11 +1647,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121003077</v>
+        <v>121002784</v>
       </c>
       <c r="B11" t="n">
-        <v>79718</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550156</v>
+        <v>550165</v>
       </c>
       <c r="R11" t="n">
-        <v>6994109</v>
+        <v>6994154</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1748,11 +1753,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121003046</v>
+        <v>121003233</v>
       </c>
       <c r="B12" t="n">
-        <v>79682</v>
+        <v>90662</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,25 +1792,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550156</v>
+        <v>550151</v>
       </c>
       <c r="R12" t="n">
-        <v>6994109</v>
+        <v>6994084</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1859,11 +1859,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121001781</v>
+        <v>121002972</v>
       </c>
       <c r="B13" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,21 +1902,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1929,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550136</v>
+        <v>550152</v>
       </c>
       <c r="R13" t="n">
-        <v>6994142</v>
+        <v>6994109</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1974,7 +1969,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121003793</v>
+        <v>121003077</v>
       </c>
       <c r="B14" t="n">
-        <v>79682</v>
+        <v>79718</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2014,25 +2009,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550193</v>
+        <v>550156</v>
       </c>
       <c r="R14" t="n">
-        <v>6994068</v>
+        <v>6994109</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2085,7 +2080,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121002784</v>
+        <v>121001781</v>
       </c>
       <c r="B15" t="n">
-        <v>90697</v>
+        <v>79682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,21 +2124,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550165</v>
+        <v>550136</v>
       </c>
       <c r="R15" t="n">
-        <v>6994154</v>
+        <v>6994142</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2192,6 +2187,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121002900</v>
+        <v>121004243</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550164</v>
+        <v>550240</v>
       </c>
       <c r="R16" t="n">
-        <v>6994129</v>
+        <v>6994134</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121002972</v>
+        <v>121001866</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,25 +2337,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550152</v>
+        <v>550136</v>
       </c>
       <c r="R17" t="n">
-        <v>6994109</v>
+        <v>6994142</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På asp tillsammans med lunglav</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,7 +2542,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121003525</v>
+        <v>121004238</v>
       </c>
       <c r="B19" t="n">
         <v>98081</v>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550173</v>
+        <v>550211</v>
       </c>
       <c r="R19" t="n">
-        <v>6994064</v>
+        <v>6994140</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121003368</v>
+        <v>121003525</v>
       </c>
       <c r="B20" t="n">
         <v>98081</v>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550164</v>
+        <v>550173</v>
       </c>
       <c r="R20" t="n">
-        <v>6994073</v>
+        <v>6994064</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121002529</v>
+        <v>121002758</v>
       </c>
       <c r="B21" t="n">
         <v>98081</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550155</v>
+        <v>550165</v>
       </c>
       <c r="R21" t="n">
-        <v>6994168</v>
+        <v>6994154</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2836,11 +2836,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rik förekomst inom ca 1 x 1 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,7 +2863,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121002758</v>
+        <v>121002529</v>
       </c>
       <c r="B22" t="n">
         <v>98081</v>
@@ -2912,10 +2907,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550165</v>
+        <v>550155</v>
       </c>
       <c r="R22" t="n">
-        <v>6994154</v>
+        <v>6994168</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2948,6 +2943,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rik förekomst inom ca 1 x 1 meter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,7 +2975,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004238</v>
+        <v>121004113</v>
       </c>
       <c r="B23" t="n">
         <v>98081</v>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550211</v>
+        <v>550183</v>
       </c>
       <c r="R23" t="n">
-        <v>6994140</v>
+        <v>6994078</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121004113</v>
+        <v>121003368</v>
       </c>
       <c r="B24" t="n">
         <v>98081</v>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550183</v>
+        <v>550164</v>
       </c>
       <c r="R24" t="n">
-        <v>6994078</v>
+        <v>6994073</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121004241</v>
+        <v>121003824</v>
       </c>
       <c r="B25" t="n">
-        <v>90983</v>
+        <v>79717</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3201,25 +3201,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550240</v>
+        <v>550193</v>
       </c>
       <c r="R25" t="n">
-        <v>6994134</v>
+        <v>6994068</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3268,6 +3268,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3295,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121003824</v>
+        <v>121004241</v>
       </c>
       <c r="B26" t="n">
-        <v>79717</v>
+        <v>90983</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3307,25 +3312,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3338,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550193</v>
+        <v>550240</v>
       </c>
       <c r="R26" t="n">
-        <v>6994068</v>
+        <v>6994134</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3374,11 +3379,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121003623</v>
+        <v>121001617</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550173</v>
+        <v>550137</v>
       </c>
       <c r="R3" t="n">
-        <v>6994058</v>
+        <v>6994152</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,11 +875,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121003793</v>
+        <v>121003973</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550193</v>
+        <v>550184</v>
       </c>
       <c r="R4" t="n">
-        <v>6994068</v>
+        <v>6994074</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,11 +981,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121003046</v>
+        <v>121002972</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,7 +1051,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550156</v>
+        <v>550152</v>
       </c>
       <c r="R5" t="n">
         <v>6994109</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121002900</v>
+        <v>121002784</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550164</v>
+        <v>550165</v>
       </c>
       <c r="R6" t="n">
-        <v>6994129</v>
+        <v>6994154</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1235,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121003862</v>
+        <v>121001781</v>
       </c>
       <c r="B7" t="n">
-        <v>79711</v>
+        <v>79685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550193</v>
+        <v>550136</v>
       </c>
       <c r="R7" t="n">
-        <v>6994068</v>
+        <v>6994142</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1318,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121003107</v>
+        <v>121002081</v>
       </c>
       <c r="B8" t="n">
-        <v>79642</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550156</v>
+        <v>550141</v>
       </c>
       <c r="R8" t="n">
-        <v>6994109</v>
+        <v>6994157</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121002081</v>
+        <v>121003623</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550141</v>
+        <v>550173</v>
       </c>
       <c r="R9" t="n">
-        <v>6994157</v>
+        <v>6994058</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,7 +1530,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121001617</v>
+        <v>121003107</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>79645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,25 +1570,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550137</v>
+        <v>550156</v>
       </c>
       <c r="R10" t="n">
-        <v>6994152</v>
+        <v>6994109</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1647,6 +1637,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121002784</v>
+        <v>121003793</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1685,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1717,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550165</v>
+        <v>550193</v>
       </c>
       <c r="R11" t="n">
-        <v>6994154</v>
+        <v>6994068</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,6 +1748,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121003233</v>
+        <v>121003862</v>
       </c>
       <c r="B12" t="n">
-        <v>90662</v>
+        <v>79714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,21 +1796,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550151</v>
+        <v>550193</v>
       </c>
       <c r="R12" t="n">
-        <v>6994084</v>
+        <v>6994068</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1859,6 +1859,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121002972</v>
+        <v>121003046</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1929,7 +1934,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550152</v>
+        <v>550156</v>
       </c>
       <c r="R13" t="n">
         <v>6994109</v>
@@ -1969,7 +1974,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121003077</v>
+        <v>121001866</v>
       </c>
       <c r="B14" t="n">
-        <v>79718</v>
+        <v>79714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2018,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550156</v>
+        <v>550136</v>
       </c>
       <c r="R14" t="n">
-        <v>6994109</v>
+        <v>6994142</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2080,7 +2085,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På asp tillsammans med lunglav</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121001781</v>
+        <v>121003077</v>
       </c>
       <c r="B15" t="n">
-        <v>79682</v>
+        <v>79721</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,25 +2125,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550136</v>
+        <v>550156</v>
       </c>
       <c r="R15" t="n">
-        <v>6994142</v>
+        <v>6994109</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2222,7 +2227,7 @@
         <v>121004243</v>
       </c>
       <c r="B16" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121001866</v>
+        <v>121002900</v>
       </c>
       <c r="B17" t="n">
-        <v>79711</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,25 +2342,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2368,10 +2373,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550136</v>
+        <v>550164</v>
       </c>
       <c r="R17" t="n">
-        <v>6994142</v>
+        <v>6994129</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2404,11 +2409,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På asp tillsammans med lunglav</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2436,10 +2436,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121003973</v>
+        <v>121003233</v>
       </c>
       <c r="B18" t="n">
-        <v>79682</v>
+        <v>90674</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2448,25 +2448,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550184</v>
+        <v>550151</v>
       </c>
       <c r="R18" t="n">
-        <v>6994074</v>
+        <v>6994084</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121004238</v>
+        <v>121003525</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550211</v>
+        <v>550173</v>
       </c>
       <c r="R19" t="n">
-        <v>6994140</v>
+        <v>6994064</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121003525</v>
+        <v>121002758</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550173</v>
+        <v>550165</v>
       </c>
       <c r="R20" t="n">
-        <v>6994064</v>
+        <v>6994154</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121002758</v>
+        <v>121003368</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550165</v>
+        <v>550164</v>
       </c>
       <c r="R21" t="n">
-        <v>6994154</v>
+        <v>6994073</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2866,7 +2866,7 @@
         <v>121002529</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004113</v>
+        <v>121004238</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550183</v>
+        <v>550211</v>
       </c>
       <c r="R23" t="n">
-        <v>6994078</v>
+        <v>6994140</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3082,10 +3082,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121003368</v>
+        <v>121004113</v>
       </c>
       <c r="B24" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550164</v>
+        <v>550183</v>
       </c>
       <c r="R24" t="n">
-        <v>6994073</v>
+        <v>6994078</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121003824</v>
+        <v>121004241</v>
       </c>
       <c r="B25" t="n">
-        <v>79717</v>
+        <v>90995</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3201,25 +3201,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550193</v>
+        <v>550240</v>
       </c>
       <c r="R25" t="n">
-        <v>6994068</v>
+        <v>6994134</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3268,11 +3268,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3295,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121004241</v>
+        <v>121003824</v>
       </c>
       <c r="B26" t="n">
-        <v>90983</v>
+        <v>79720</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3312,25 +3307,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3343,10 +3338,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550240</v>
+        <v>550193</v>
       </c>
       <c r="R26" t="n">
-        <v>6994134</v>
+        <v>6994068</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3379,6 +3374,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -2542,10 +2542,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121003525</v>
+        <v>121004238</v>
       </c>
       <c r="B19" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550173</v>
+        <v>550211</v>
       </c>
       <c r="R19" t="n">
-        <v>6994064</v>
+        <v>6994140</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2652,7 +2652,7 @@
         <v>121002758</v>
       </c>
       <c r="B20" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121003368</v>
+        <v>121002529</v>
       </c>
       <c r="B21" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550164</v>
+        <v>550155</v>
       </c>
       <c r="R21" t="n">
-        <v>6994073</v>
+        <v>6994168</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2836,6 +2836,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rik förekomst inom ca 1 x 1 meter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,10 +2868,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121002529</v>
+        <v>121003525</v>
       </c>
       <c r="B22" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2907,10 +2912,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550155</v>
+        <v>550173</v>
       </c>
       <c r="R22" t="n">
-        <v>6994168</v>
+        <v>6994064</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2943,11 +2948,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rik förekomst inom ca 1 x 1 meter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121004238</v>
+        <v>121003368</v>
       </c>
       <c r="B23" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550211</v>
+        <v>550164</v>
       </c>
       <c r="R23" t="n">
-        <v>6994140</v>
+        <v>6994073</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3085,7 +3085,7 @@
         <v>121004113</v>
       </c>
       <c r="B24" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>121004241</v>
       </c>
       <c r="B25" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -3192,7 +3192,7 @@
         <v>121004241</v>
       </c>
       <c r="B25" t="n">
-        <v>90996</v>
+        <v>90999</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>121003824</v>
       </c>
       <c r="B26" t="n">
-        <v>79720</v>
+        <v>79723</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3404,6 +3404,596 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134246399</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80478</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>550158</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6994115</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134246404</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>550235</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6994071</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134246406</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99200</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>550277</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6994166</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134246400</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80423</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>550158</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6994115</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134246395</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79358</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>550292</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6994150</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134246401</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80473</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>550158</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6994115</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>134246399</v>
       </c>
       <c r="B27" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>134246406</v>
       </c>
       <c r="B29" t="n">
-        <v>99200</v>
+        <v>99202</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>134246400</v>
       </c>
       <c r="B30" t="n">
-        <v>80423</v>
+        <v>80424</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>134246395</v>
       </c>
       <c r="B31" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>134246401</v>
       </c>
       <c r="B32" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -3409,7 +3409,7 @@
         <v>134246399</v>
       </c>
       <c r="B27" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>134246406</v>
       </c>
       <c r="B29" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>134246400</v>
       </c>
       <c r="B30" t="n">
-        <v>80424</v>
+        <v>80431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>134246395</v>
       </c>
       <c r="B31" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>134246401</v>
       </c>
       <c r="B32" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103996148</v>
+        <v>121002217</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blomkindtjärnen V, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550236.4140847964</v>
+        <v>550145</v>
       </c>
       <c r="R2" t="n">
-        <v>6994139.421352408</v>
+        <v>6994163</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,13 +757,9 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,26 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121001617</v>
+        <v>121004241</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550137</v>
+        <v>550240</v>
       </c>
       <c r="R3" t="n">
-        <v>6994152</v>
+        <v>6994134</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121003973</v>
+        <v>103996148</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,40 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550184</v>
+        <v>550237</v>
       </c>
       <c r="R4" t="n">
-        <v>6994074</v>
+        <v>6994140</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,12 +942,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,9 +966,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,22 +982,21 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121002972</v>
+        <v>121002233</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550152</v>
+        <v>550145</v>
       </c>
       <c r="R5" t="n">
-        <v>6994109</v>
+        <v>6994163</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,12 +1097,7 @@
         <v>121002784</v>
       </c>
       <c r="B6" t="n">
-        <v>90709</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,15 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121001781</v>
+        <v>121004243</v>
       </c>
       <c r="B7" t="n">
-        <v>79685</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550136</v>
+        <v>550240</v>
       </c>
       <c r="R7" t="n">
-        <v>6994142</v>
+        <v>6994134</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1304,11 +1269,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,56 +1296,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121002081</v>
+        <v>103996059</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550141</v>
+        <v>550310</v>
       </c>
       <c r="R8" t="n">
-        <v>6994157</v>
+        <v>6994183</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,17 +1361,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fertil</t>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,9 +1385,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1440,22 +1401,21 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121003623</v>
+        <v>134246391</v>
       </c>
       <c r="B9" t="n">
-        <v>79685</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,40 +1423,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Blomkindtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550173</v>
+        <v>550317</v>
       </c>
       <c r="R9" t="n">
-        <v>6994058</v>
+        <v>6994117</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,17 +1477,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,34 +1491,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121003107</v>
+        <v>121003233</v>
       </c>
       <c r="B10" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,21 +1520,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550156</v>
+        <v>550151</v>
       </c>
       <c r="R10" t="n">
-        <v>6994109</v>
+        <v>6994084</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1637,11 +1583,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,37 +1610,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121003793</v>
+        <v>121001372</v>
       </c>
       <c r="B11" t="n">
-        <v>79685</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550193</v>
+        <v>550123</v>
       </c>
       <c r="R11" t="n">
-        <v>6994068</v>
+        <v>6994147</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1748,11 +1684,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,37 +1711,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121003862</v>
+        <v>121001617</v>
       </c>
       <c r="B12" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1823,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550193</v>
+        <v>550137</v>
       </c>
       <c r="R12" t="n">
-        <v>6994068</v>
+        <v>6994152</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1859,11 +1785,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,37 +1812,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121003046</v>
+        <v>121002081</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1934,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550156</v>
+        <v>550141</v>
       </c>
       <c r="R13" t="n">
-        <v>6994109</v>
+        <v>6994157</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1974,7 +1890,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2002,37 +1918,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121001866</v>
+        <v>121002900</v>
       </c>
       <c r="B14" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550136</v>
+        <v>550164</v>
       </c>
       <c r="R14" t="n">
-        <v>6994142</v>
+        <v>6994129</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2081,11 +1992,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På asp tillsammans med lunglav</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,37 +2019,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121003077</v>
+        <v>121002972</v>
       </c>
       <c r="B15" t="n">
-        <v>79721</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,7 +2057,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550156</v>
+        <v>550152</v>
       </c>
       <c r="R15" t="n">
         <v>6994109</v>
@@ -2196,7 +2097,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2224,37 +2125,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121004243</v>
+        <v>121004337</v>
       </c>
       <c r="B16" t="n">
-        <v>90709</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2267,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550240</v>
+        <v>550319</v>
       </c>
       <c r="R16" t="n">
-        <v>6994134</v>
+        <v>6994143</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2303,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,19 +2231,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121002900</v>
+        <v>134246395</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2364,22 +2260,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550164</v>
+        <v>550292</v>
       </c>
       <c r="R17" t="n">
-        <v>6994129</v>
+        <v>6994150</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2403,12 +2296,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,56 +2310,50 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121003233</v>
+        <v>121001781</v>
       </c>
       <c r="B18" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2479,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550151</v>
+        <v>550136</v>
       </c>
       <c r="R18" t="n">
-        <v>6994084</v>
+        <v>6994142</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2515,6 +2402,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,43 +2434,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121004238</v>
+        <v>121003046</v>
       </c>
       <c r="B19" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2586,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550211</v>
+        <v>550156</v>
       </c>
       <c r="R19" t="n">
-        <v>6994140</v>
+        <v>6994109</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2622,6 +2508,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,43 +2540,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121002758</v>
+        <v>121003623</v>
       </c>
       <c r="B20" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2693,10 +2578,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550165</v>
+        <v>550173</v>
       </c>
       <c r="R20" t="n">
-        <v>6994154</v>
+        <v>6994058</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2729,6 +2614,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,43 +2646,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121002529</v>
+        <v>121003793</v>
       </c>
       <c r="B21" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2800,10 +2684,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550155</v>
+        <v>550193</v>
       </c>
       <c r="R21" t="n">
-        <v>6994168</v>
+        <v>6994068</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2840,7 +2724,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rik förekomst inom ca 1 x 1 meter.</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,43 +2752,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121003525</v>
+        <v>121003973</v>
       </c>
       <c r="B22" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2912,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550173</v>
+        <v>550184</v>
       </c>
       <c r="R22" t="n">
-        <v>6994064</v>
+        <v>6994074</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2975,57 +2853,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121003368</v>
+        <v>134246401</v>
       </c>
       <c r="B23" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550164</v>
+        <v>550158</v>
       </c>
       <c r="R23" t="n">
-        <v>6994073</v>
+        <v>6994115</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3049,12 +2918,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3063,62 +2932,55 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121004113</v>
+        <v>121001866</v>
       </c>
       <c r="B24" t="n">
-        <v>98095</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3126,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550183</v>
+        <v>550136</v>
       </c>
       <c r="R24" t="n">
-        <v>6994078</v>
+        <v>6994142</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3162,6 +3024,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På asp tillsammans med lunglav</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,37 +3056,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121004241</v>
+        <v>121003862</v>
       </c>
       <c r="B25" t="n">
-        <v>90999</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3094,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550240</v>
+        <v>550193</v>
       </c>
       <c r="R25" t="n">
-        <v>6994134</v>
+        <v>6994068</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3268,6 +3130,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3295,15 +3162,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121003824</v>
+        <v>134246399</v>
       </c>
       <c r="B26" t="n">
-        <v>79723</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80493</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,40 +3173,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomkind, Jmt</t>
+          <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550193</v>
+        <v>550158</v>
       </c>
       <c r="R26" t="n">
-        <v>6994068</v>
+        <v>6994115</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3368,17 +3227,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,29 +3241,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134246399</v>
+        <v>121003824</v>
       </c>
       <c r="B27" t="n">
-        <v>80486</v>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,37 +3270,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550158</v>
+        <v>550193</v>
       </c>
       <c r="R27" t="n">
-        <v>6994115</v>
+        <v>6994068</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3471,12 +3327,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,74 +3346,70 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134246404</v>
+        <v>121003077</v>
       </c>
       <c r="B28" t="n">
-        <v>58461</v>
+        <v>80468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103018</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550235</v>
+        <v>550156</v>
       </c>
       <c r="R28" t="n">
-        <v>6994071</v>
+        <v>6994109</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3576,12 +3433,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3590,28 +3452,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134246406</v>
+        <v>121001246</v>
       </c>
       <c r="B29" t="n">
-        <v>99210</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3619,37 +3482,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550277</v>
+        <v>550118</v>
       </c>
       <c r="R29" t="n">
-        <v>6994166</v>
+        <v>6994138</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3673,19 +3544,24 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Kraftigt bearbetad grov låga, troligen av spillkråka.</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3693,22 +3569,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134246400</v>
+        <v>134246404</v>
       </c>
       <c r="B30" t="n">
-        <v>80431</v>
+        <v>58461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,34 +3592,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>103018</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lapprännbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550158</v>
+        <v>550235</v>
       </c>
       <c r="R30" t="n">
-        <v>6994115</v>
+        <v>6994071</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,48 +3686,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134246395</v>
+        <v>121002529</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550292</v>
+        <v>550155</v>
       </c>
       <c r="R31" t="n">
-        <v>6994150</v>
+        <v>6994168</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3867,12 +3755,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rik förekomst inom ca 1 x 1 meter.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3881,66 +3774,71 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134246401</v>
+        <v>121002758</v>
       </c>
       <c r="B32" t="n">
-        <v>80481</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lapprännbäcken, Jmt</t>
+          <t>Blomkind, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550158</v>
+        <v>550165</v>
       </c>
       <c r="R32" t="n">
-        <v>6994115</v>
+        <v>6994154</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3964,12 +3862,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3978,21 +3876,832 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121003368</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>550164</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6994073</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121003525</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>550173</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6994064</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121004113</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>550183</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6994078</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121004238</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>550211</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6994140</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121004332</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>550310</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6994126</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134246406</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>550277</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6994166</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX38" t="inlineStr">
         <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121003107</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Blomkind, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>550156</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6994109</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134246400</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lapprännbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>550158</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6994115</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41412-2024 artfynd.xlsx
+++ b/artfynd/A 41412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121002217</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004241</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996148</t>
         </is>
       </c>
     </row>
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121002233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121002784</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004243</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996059</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246391</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1607,6 +1652,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003233</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121001372</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121001617</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1915,6 +1975,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121002081</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2016,6 +2081,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121002900</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121002972</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2228,6 +2303,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004337</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2325,6 +2405,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246395</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2431,6 +2516,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121001781</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2537,6 +2627,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003046</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2643,6 +2738,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003623</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2749,6 +2849,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003793</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2850,6 +2955,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003973</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2947,6 +3057,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246401</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3053,6 +3168,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121001866</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3159,6 +3279,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003862</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3256,6 +3381,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246399</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3362,6 +3492,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003824</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3468,6 +3603,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003077</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3578,6 +3718,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121001246</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3683,6 +3828,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246404</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3790,6 +3940,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121002529</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3892,6 +4047,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121002758</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3994,6 +4154,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003368</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4096,6 +4261,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003525</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4198,6 +4368,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004113</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4300,6 +4475,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004238</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4402,6 +4582,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121004332</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4499,6 +4684,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246406</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4605,6 +4795,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121003107</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4702,8 +4897,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246400</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>